--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T06:41:33+00:00</t>
+    <t>2024-01-12T11:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T11:46:53+00:00</t>
+    <t>2024-01-12T11:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T18:58:49+00:00</t>
+    <t>2024-03-12T11:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$80</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.2</t>
+    <t>0.8.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T06:42:57+00:00</t>
+    <t>2024-03-15T09:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,156 +419,113 @@
     <t>Practitioner.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Practitioner.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>practitioner:identifier and practitioner:hpr-nr</t>
+  </si>
+  <si>
+    <t>An identifier that applies to this person in this role.</t>
+  </si>
+  <si>
+    <t>Often, specific identities are assigned for the agent.</t>
+  </si>
+  <si>
+    <t>PRD-7 (or XCN.1)</t>
+  </si>
+  <si>
+    <t>./id</t>
+  </si>
+  <si>
+    <t>./Identifiers</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber</t>
-  </si>
-  <si>
-    <t>_HPRNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {elementdefinition-identifier}
-</t>
-  </si>
-  <si>
-    <t>External Identifier associated with this element</t>
-  </si>
-  <si>
-    <t>External Identifiers associated with this element - these are identifiers that are associated with the concept this element represents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Act.id, Role.id, Entity.id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.url</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/elementdefinition-identifier</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].extension</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].use</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].use</t>
+    <t>Practitioner.identifier.use</t>
   </si>
   <si>
     <t>usual | official | temp | secondary | old (If known)</t>
@@ -601,10 +555,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].type</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].type</t>
+    <t>Practitioner.identifier.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -638,13 +589,10 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].system</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].system</t>
-  </si>
-  <si>
-    <t>practitioner:hpr-nr:system</t>
+    <t>Practitioner.identifier.system</t>
+  </si>
+  <si>
+    <t>practitioner:identifier:system and practitioner:hpr-nr:system</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -671,13 +619,10 @@
     <t>./IdentifierType</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].value</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].value</t>
-  </si>
-  <si>
-    <t>practitioner:hpr-nr:id</t>
+    <t>Practitioner.identifier.value</t>
+  </si>
+  <si>
+    <t>practitioner:identifier:id and practitioner:hpr-nr:id</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -701,10 +646,7 @@
     <t>./Value</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].period</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].period</t>
+    <t>Practitioner.identifier.period</t>
   </si>
   <si>
     <t xml:space="preserve">Period
@@ -729,10 +671,7 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner</t>
+    <t>Practitioner.identifier.assigner</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Organization)
@@ -760,22 +699,13 @@
     <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.reference</t>
+    <t>Practitioner.identifier.assigner.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.assigner.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.assigner.reference</t>
   </si>
   <si>
     <t>Literal reference, Relative, internal or absolute URL</t>
@@ -794,10 +724,7 @@
 </t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.type</t>
+    <t>Practitioner.identifier.assigner.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -819,10 +746,7 @@
     <t>Reference.type</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.identifier</t>
+    <t>Practitioner.identifier.assigner.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -843,13 +767,10 @@
     <t>.identifier</t>
   </si>
   <si>
-    <t>Practitioner.extension:_HPRNumber.value[x].assigner.display</t>
-  </si>
-  <si>
-    <t>Practitioner.extension.value[x].assigner.display</t>
-  </si>
-  <si>
-    <t>practitioner:hpr-nr:authority</t>
+    <t>Practitioner.identifier.assigner.display</t>
+  </si>
+  <si>
+    <t>practitioner:identifier:authority and practitioner:hpr-nr:authority</t>
   </si>
   <si>
     <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
@@ -859,97 +780,6 @@
   </si>
   <si>
     <t>Reference.display</t>
-  </si>
-  <si>
-    <t>Practitioner.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier</t>
-  </si>
-  <si>
-    <t>An identifier for the person as this agent</t>
-  </si>
-  <si>
-    <t>An identifier that applies to this person in this role.</t>
-  </si>
-  <si>
-    <t>Often, specific identities are assigned for the agent.</t>
-  </si>
-  <si>
-    <t>PRD-7 (or XCN.1)</t>
-  </si>
-  <si>
-    <t>./id</t>
-  </si>
-  <si>
-    <t>./Identifiers</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.use</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.system</t>
-  </si>
-  <si>
-    <t>practitioner:identifier:system</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.value</t>
-  </si>
-  <si>
-    <t>practitioner:identifier:id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.period</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner.display</t>
-  </si>
-  <si>
-    <t>practitioner:identifier:authority</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1762,21 +1592,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1942,12 +1757,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN80"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.75" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.75" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.08203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1955,7 +1770,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="38.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2108,7 +1923,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -2220,7 +2035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -2334,7 +2149,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>93</v>
       </c>
@@ -2446,7 +2261,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>99</v>
       </c>
@@ -2560,7 +2375,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>105</v>
       </c>
@@ -2674,7 +2489,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2788,7 +2603,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2902,7 +2717,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>130</v>
       </c>
@@ -2911,7 +2726,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2930,15 +2745,17 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>75</v>
@@ -2975,14 +2792,16 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -3003,7 +2822,7 @@
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>75</v>
@@ -3012,46 +2831,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>75</v>
       </c>
@@ -3099,7 +2920,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3108,17 +2929,17 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="AL10" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="AM10" t="s" s="2">
         <v>75</v>
       </c>
@@ -3126,12 +2947,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3142,7 +2963,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -3151,19 +2972,21 @@
         <v>75</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
       </c>
@@ -3211,39 +3034,39 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AM11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>75</v>
-      </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3254,7 +3077,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -3266,13 +3089,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3311,37 +3134,37 @@
         <v>75</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>75</v>
@@ -3350,23 +3173,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>75</v>
@@ -3378,16 +3201,16 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3395,67 +3218,67 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AC13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>75</v>
@@ -3464,9 +3287,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>164</v>
@@ -3477,7 +3300,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>86</v>
@@ -3486,22 +3309,26 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
       </c>
@@ -3525,13 +3352,13 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -3549,7 +3376,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3564,10 +3391,10 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>75</v>
@@ -3576,12 +3403,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3601,19 +3428,23 @@
         <v>75</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>75</v>
       </c>
@@ -3637,13 +3468,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3661,7 +3492,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3673,13 +3504,13 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>75</v>
@@ -3688,23 +3519,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>75</v>
@@ -3713,21 +3544,23 @@
         <v>75</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
       </c>
@@ -3739,7 +3572,7 @@
         <v>75</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>75</v>
@@ -3763,51 +3596,51 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3824,26 +3657,24 @@
         <v>75</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>75</v>
       </c>
@@ -3855,7 +3686,7 @@
         <v>75</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>75</v>
@@ -3867,13 +3698,13 @@
         <v>75</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>75</v>
@@ -3891,7 +3722,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3906,24 +3737,24 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3946,20 +3777,16 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -3983,13 +3810,13 @@
         <v>75</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>75</v>
@@ -4007,7 +3834,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4022,24 +3849,24 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4062,20 +3889,18 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
       </c>
@@ -4087,7 +3912,7 @@
         <v>75</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>75</v>
@@ -4123,7 +3948,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4138,24 +3963,24 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4175,20 +4000,18 @@
         <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -4201,7 +4024,7 @@
         <v>75</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>75</v>
@@ -4237,7 +4060,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4249,38 +4072,38 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4289,18 +4112,20 @@
         <v>75</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>133</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -4337,51 +4162,51 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4404,16 +4229,16 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4463,7 +4288,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4472,30 +4297,30 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>129</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4515,18 +4340,20 @@
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4551,13 +4378,13 @@
         <v>75</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>75</v>
+        <v>233</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>75</v>
@@ -4575,7 +4402,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4587,13 +4414,13 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
@@ -4602,23 +4429,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
@@ -4627,19 +4454,19 @@
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4677,37 +4504,37 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -4716,12 +4543,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4744,16 +4571,16 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4803,7 +4630,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4812,7 +4639,7 @@
         <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4830,12 +4657,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4858,22 +4685,26 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>100</v>
+        <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="P26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4893,13 +4724,13 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>256</v>
+        <v>75</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4917,7 +4748,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4935,21 +4766,21 @@
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4960,7 +4791,7 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4972,18 +4803,20 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -5031,13 +4864,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
@@ -5046,24 +4879,24 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5083,20 +4916,18 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -5145,7 +4976,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>156</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5157,13 +4988,13 @@
         <v>75</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -5172,16 +5003,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5194,26 +5025,24 @@
         <v>75</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>159</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -5249,19 +5078,19 @@
         <v>75</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5279,7 +5108,7 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -5288,12 +5117,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5304,29 +5133,31 @@
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5351,13 +5182,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5375,13 +5206,13 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
@@ -5390,24 +5221,24 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5427,19 +5258,23 @@
         <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
@@ -5487,7 +5322,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5499,13 +5334,13 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>151</v>
+        <v>285</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>75</v>
@@ -5514,7 +5349,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>286</v>
       </c>
@@ -5523,14 +5358,14 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -5539,19 +5374,19 @@
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>174</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5589,87 +5424,85 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>155</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>75</v>
+        <v>292</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>151</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -5693,13 +5526,13 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5717,13 +5550,13 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>186</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
@@ -5732,24 +5565,24 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>129</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5760,7 +5593,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -5772,20 +5605,16 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -5809,13 +5638,13 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5833,13 +5662,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5848,24 +5677,24 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5876,7 +5705,7 @@
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -5888,20 +5717,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5913,7 +5738,7 @@
         <v>75</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>75</v>
@@ -5949,13 +5774,13 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>207</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
@@ -5964,24 +5789,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6004,18 +5829,18 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -6027,7 +5852,7 @@
         <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>75</v>
@@ -6063,7 +5888,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6078,24 +5903,24 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>218</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>219</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6106,7 +5931,7 @@
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -6118,16 +5943,20 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>224</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -6175,13 +6004,13 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>226</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>75</v>
@@ -6190,24 +6019,24 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>227</v>
+        <v>330</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>228</v>
+        <v>331</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>229</v>
+        <v>332</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6218,7 +6047,7 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -6230,18 +6059,20 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>232</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>233</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>234</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -6289,13 +6120,13 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
@@ -6304,24 +6135,24 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>239</v>
+        <v>341</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6341,19 +6172,21 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>148</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>149</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -6377,13 +6210,13 @@
         <v>75</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -6401,7 +6234,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>150</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6413,38 +6246,38 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>151</v>
+        <v>349</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -6453,21 +6286,21 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>131</v>
+        <v>352</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>174</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -6503,51 +6336,51 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>155</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>151</v>
+        <v>357</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>75</v>
+        <v>358</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6558,7 +6391,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -6567,21 +6400,21 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>246</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6629,16 +6462,16 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
@@ -6647,21 +6480,21 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>129</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>75</v>
+        <v>365</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6672,7 +6505,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6681,20 +6514,18 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>100</v>
+        <v>367</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>253</v>
+        <v>368</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6719,13 +6550,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>256</v>
+        <v>75</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6743,13 +6574,13 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>258</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -6758,24 +6589,24 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>371</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>75</v>
+        <v>372</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6795,20 +6626,18 @@
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6857,7 +6686,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6869,13 +6698,13 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6884,23 +6713,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -6909,19 +6738,19 @@
         <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>301</v>
+        <v>133</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>270</v>
+        <v>135</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6971,25 +6800,25 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -6998,54 +6827,52 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>302</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>303</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>307</v>
+        <v>141</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>75</v>
       </c>
@@ -7089,39 +6916,39 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>310</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7141,22 +6968,20 @@
         <v>75</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>312</v>
+        <v>144</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>316</v>
+        <v>383</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -7205,7 +7030,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7220,24 +7045,24 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>317</v>
+        <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>319</v>
+        <v>75</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7245,7 +7070,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>86</v>
@@ -7260,13 +7085,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>148</v>
+        <v>386</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>149</v>
+        <v>387</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7293,13 +7118,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>75</v>
+        <v>388</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -7317,10 +7142,10 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>150</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>86</v>
@@ -7329,38 +7154,38 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>151</v>
+        <v>371</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>75</v>
+        <v>391</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -7372,17 +7197,15 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7419,37 +7242,37 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
@@ -7458,48 +7281,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>323</v>
+        <v>133</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>324</v>
+        <v>159</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7523,63 +7344,63 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>327</v>
+        <v>75</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>328</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>329</v>
+        <v>163</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>331</v>
+        <v>157</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>332</v>
+        <v>75</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7590,7 +7411,7 @@
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -7602,19 +7423,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>147</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>334</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7663,13 +7484,13 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
@@ -7678,10 +7499,10 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
@@ -7690,16 +7511,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>342</v>
+        <v>75</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7715,20 +7536,18 @@
         <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>343</v>
+        <v>154</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7777,7 +7596,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>156</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7789,31 +7608,31 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>347</v>
+        <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>348</v>
+        <v>157</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>349</v>
+        <v>75</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7829,19 +7648,19 @@
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>353</v>
+        <v>159</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>354</v>
+        <v>135</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7879,19 +7698,19 @@
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>163</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7903,27 +7722,27 @@
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>357</v>
+        <v>157</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>358</v>
+        <v>75</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7934,7 +7753,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -7946,16 +7765,20 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
       </c>
@@ -8003,13 +7826,13 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>75</v>
@@ -8018,24 +7841,24 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8046,7 +7869,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -8058,15 +7881,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8115,13 +7940,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -8130,10 +7955,10 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>75</v>
@@ -8142,12 +7967,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8170,17 +7995,17 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8229,7 +8054,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8244,24 +8069,24 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>377</v>
+        <v>425</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8272,7 +8097,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -8284,19 +8109,17 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>380</v>
+        <v>153</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>428</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8345,13 +8168,13 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
@@ -8360,24 +8183,24 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>385</v>
+        <v>432</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>387</v>
+        <v>75</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8388,7 +8211,7 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -8400,19 +8223,19 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>248</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>435</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
+        <v>436</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>392</v>
+        <v>437</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>393</v>
+        <v>438</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8461,13 +8284,13 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
@@ -8476,24 +8299,24 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>396</v>
+        <v>75</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8516,17 +8339,19 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -8551,13 +8376,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>401</v>
+        <v>75</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>402</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -8575,7 +8400,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8590,24 +8415,24 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>405</v>
+        <v>75</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8627,20 +8452,20 @@
         <v>75</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>407</v>
+        <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8689,7 +8514,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8704,24 +8529,24 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8732,7 +8557,7 @@
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8744,18 +8569,16 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>415</v>
+        <v>213</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>75</v>
       </c>
@@ -8803,13 +8626,13 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>75</v>
@@ -8821,21 +8644,21 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8858,16 +8681,20 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>422</v>
+        <v>175</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -8891,13 +8718,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8915,7 +8742,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8930,2205 +8757,19 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AN80" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN80">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI79">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>
